--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/08,26/31,08,26 Останкино КИ и ЗПФ/машины Останкино КИ и ЗПФ.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/08,26/31,08,26 Останкино КИ и ЗПФ/машины Останкино КИ и ЗПФ.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\08,26\31,08,26 Останкино КИ и ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D3B6EBD-E37D-438D-B467-F3A13AECB17D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09D98C57-14E6-433B-BB1B-CA25E146DD7E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="27">
   <si>
     <t>Бердянск</t>
   </si>
@@ -109,6 +109,9 @@
   </si>
   <si>
     <t>ПРС</t>
+  </si>
+  <si>
+    <t>Бердянск дозаказ</t>
   </si>
 </sst>
 </file>
@@ -550,7 +553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
@@ -627,7 +630,7 @@
         <v>7893</v>
       </c>
       <c r="F4" s="6">
-        <f t="shared" ref="F4:F13" si="1">B4-C4-D4-E4</f>
+        <f t="shared" ref="F4:F14" si="1">B4-C4-D4-E4</f>
         <v>0</v>
       </c>
       <c r="G4" s="7" t="s">
@@ -636,18 +639,18 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="B5" s="6">
-        <v>23</v>
+        <v>642</v>
       </c>
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
       <c r="E5" s="6">
-        <v>23</v>
+        <v>642</v>
       </c>
       <c r="F5" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="F5" si="2">B5-C5-D5-E5</f>
         <v>0</v>
       </c>
       <c r="G5" s="7" t="s">
@@ -655,34 +658,37 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="2">
-        <v>10067</v>
-      </c>
-      <c r="C6" s="2">
-        <v>5184</v>
-      </c>
-      <c r="D6" s="2">
-        <v>4883</v>
-      </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2">
+      <c r="A6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="6">
+        <v>23</v>
+      </c>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6">
+        <v>23</v>
+      </c>
+      <c r="F6" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B7" s="2">
-        <v>94</v>
-      </c>
-      <c r="C7" s="2"/>
+        <v>10067</v>
+      </c>
+      <c r="C7" s="2">
+        <v>5184</v>
+      </c>
       <c r="D7" s="2">
-        <v>94</v>
+        <v>4883</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2">
@@ -692,71 +698,68 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B8" s="2">
-        <v>5261</v>
+        <v>94</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2">
-        <v>5261</v>
+        <v>94</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G8" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="B9" s="2">
-        <v>357</v>
+        <v>5261</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2">
-        <v>357</v>
+        <v>5261</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="8">
-        <v>5142</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8">
-        <v>5142</v>
-      </c>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8">
+      <c r="A10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="2">
+        <v>357</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2">
+        <v>357</v>
+      </c>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="B11" s="8">
-        <v>199</v>
+        <v>5142</v>
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="8">
-        <v>199</v>
+        <v>5142</v>
       </c>
       <c r="E11" s="8"/>
       <c r="F11" s="8">
@@ -768,99 +771,119 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" s="2">
-        <v>8340</v>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2">
-        <v>8340</v>
-      </c>
-      <c r="F12" s="2">
+      <c r="A12" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="8">
+        <v>199</v>
+      </c>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8">
+        <v>199</v>
+      </c>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2">
-        <v>1755</v>
-      </c>
-      <c r="C13" s="2">
-        <v>1755</v>
-      </c>
+        <v>8340</v>
+      </c>
+      <c r="C13" s="2"/>
       <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
+      <c r="E13" s="2">
+        <v>8340</v>
+      </c>
       <c r="F13" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="2">
+        <v>1755</v>
+      </c>
+      <c r="C14" s="2">
+        <v>1755</v>
+      </c>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="4">
-        <f>SUM(B2:B13)</f>
-        <v>42259</v>
-      </c>
-      <c r="C14" s="4">
-        <f>SUM(C2:C13)</f>
+      <c r="B15" s="4">
+        <f>SUM(B2:B14)</f>
+        <v>42901</v>
+      </c>
+      <c r="C15" s="4">
+        <f>SUM(C2:C14)</f>
         <v>10067</v>
       </c>
-      <c r="D14" s="4">
-        <f>SUM(D2:D13)</f>
+      <c r="D15" s="4">
+        <f>SUM(D2:D14)</f>
         <v>15936</v>
       </c>
-      <c r="E14" s="4">
-        <f>SUM(E2:E13)</f>
-        <v>16256</v>
-      </c>
-      <c r="F14" s="4">
-        <f>SUM(F2:F13)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C15" t="s">
+      <c r="E15" s="4">
+        <f>SUM(E2:E14)</f>
+        <v>16898</v>
+      </c>
+      <c r="F15" s="4">
+        <f>SUM(F2:F14)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C16" t="s">
         <v>16</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D16" t="s">
         <v>17</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E16" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C16" s="10" t="s">
+    <row r="17" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C17" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="11"/>
-      <c r="E16" s="12"/>
-    </row>
-    <row r="17" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C17" s="3">
-        <f>IF(ROUNDUP(C14/500,0)&gt;32,32,ROUNDUP(C14/500,0))</f>
+      <c r="D17" s="11"/>
+      <c r="E17" s="12"/>
+    </row>
+    <row r="18" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C18" s="3">
+        <f>IF(ROUNDUP(C15/500,0)&gt;32,32,ROUNDUP(C15/500,0))</f>
         <v>21</v>
       </c>
-      <c r="D17" s="3">
-        <f t="shared" ref="D17:E17" si="2">IF(ROUNDUP(D14/500,0)&gt;32,32,ROUNDUP(D14/500,0))</f>
+      <c r="D18" s="3">
+        <f t="shared" ref="D18:E18" si="3">IF(ROUNDUP(D15/500,0)&gt;32,32,ROUNDUP(D15/500,0))</f>
         <v>32</v>
       </c>
-      <c r="E17" s="3">
-        <f t="shared" si="2"/>
+      <c r="E18" s="3">
+        <f t="shared" si="3"/>
         <v>32</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="C17:E17"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
